--- a/figures/APOGEE_tables.xlsx
+++ b/figures/APOGEE_tables.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="54" documentId="8_{1FD88259-38DA-4BCB-87A5-3E65E87D97B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46254CCC-B73F-4315-BC00-6755C1411836}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{782AB3F7-35A0-4D4F-8A15-6B7895E48BDD}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="17505" windowHeight="15585" activeTab="1" xr2:uid="{782AB3F7-35A0-4D4F-8A15-6B7895E48BDD}"/>
   </bookViews>
   <sheets>
     <sheet name="tab_1_sum_mock" sheetId="3" r:id="rId1"/>
@@ -408,6 +408,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -425,39 +458,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -837,7 +837,7 @@
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="37" t="s">
         <v>45</v>
       </c>
       <c r="C3" s="13" t="s">
@@ -863,7 +863,7 @@
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="27"/>
+      <c r="B4" s="38"/>
       <c r="C4" s="22" t="s">
         <v>47</v>
       </c>
@@ -887,7 +887,7 @@
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="27"/>
+      <c r="B5" s="38"/>
       <c r="C5" s="22" t="s">
         <v>48</v>
       </c>
@@ -911,7 +911,7 @@
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="27"/>
+      <c r="B6" s="38"/>
       <c r="C6" s="22" t="s">
         <v>49</v>
       </c>
@@ -935,7 +935,7 @@
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="27"/>
+      <c r="B7" s="38"/>
       <c r="C7" s="22" t="s">
         <v>50</v>
       </c>
@@ -959,7 +959,7 @@
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="27"/>
+      <c r="B8" s="38"/>
       <c r="C8" s="22" t="s">
         <v>51</v>
       </c>
@@ -983,7 +983,7 @@
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="27"/>
+      <c r="B9" s="38"/>
       <c r="C9" s="22" t="s">
         <v>52</v>
       </c>
@@ -1007,7 +1007,7 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="27"/>
+      <c r="B10" s="38"/>
       <c r="C10" s="22" t="s">
         <v>53</v>
       </c>
@@ -1031,7 +1031,7 @@
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="27"/>
+      <c r="B11" s="38"/>
       <c r="C11" s="22" t="s">
         <v>54</v>
       </c>
@@ -1055,7 +1055,7 @@
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="27"/>
+      <c r="B12" s="38"/>
       <c r="C12" s="22" t="s">
         <v>55</v>
       </c>
@@ -1079,7 +1079,7 @@
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="27"/>
+      <c r="B13" s="38"/>
       <c r="C13" s="22" t="s">
         <v>56</v>
       </c>
@@ -1103,7 +1103,7 @@
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="27"/>
+      <c r="B14" s="38"/>
       <c r="C14" s="24" t="s">
         <v>57</v>
       </c>
@@ -1127,7 +1127,7 @@
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="27"/>
+      <c r="B15" s="38"/>
       <c r="C15" s="20" t="s">
         <v>58</v>
       </c>
@@ -1154,7 +1154,7 @@
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="27"/>
+      <c r="B16" s="38"/>
       <c r="C16" s="16" t="s">
         <v>3</v>
       </c>
@@ -1181,7 +1181,7 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="28"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="17" t="s">
         <v>59</v>
       </c>
@@ -1203,7 +1203,7 @@
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="37" t="s">
         <v>60</v>
       </c>
       <c r="C18" s="13" t="s">
@@ -1229,7 +1229,7 @@
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="27"/>
+      <c r="B19" s="38"/>
       <c r="C19" s="22" t="s">
         <v>47</v>
       </c>
@@ -1253,7 +1253,7 @@
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="27"/>
+      <c r="B20" s="38"/>
       <c r="C20" s="22" t="s">
         <v>48</v>
       </c>
@@ -1277,7 +1277,7 @@
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="27"/>
+      <c r="B21" s="38"/>
       <c r="C21" s="22" t="s">
         <v>49</v>
       </c>
@@ -1301,7 +1301,7 @@
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" s="27"/>
+      <c r="B22" s="38"/>
       <c r="C22" s="22" t="s">
         <v>50</v>
       </c>
@@ -1325,7 +1325,7 @@
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B23" s="27"/>
+      <c r="B23" s="38"/>
       <c r="C23" s="22" t="s">
         <v>51</v>
       </c>
@@ -1349,7 +1349,7 @@
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="27"/>
+      <c r="B24" s="38"/>
       <c r="C24" s="22" t="s">
         <v>52</v>
       </c>
@@ -1373,7 +1373,7 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="27"/>
+      <c r="B25" s="38"/>
       <c r="C25" s="22" t="s">
         <v>53</v>
       </c>
@@ -1397,7 +1397,7 @@
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="27"/>
+      <c r="B26" s="38"/>
       <c r="C26" s="22" t="s">
         <v>54</v>
       </c>
@@ -1421,7 +1421,7 @@
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="27"/>
+      <c r="B27" s="38"/>
       <c r="C27" s="22" t="s">
         <v>55</v>
       </c>
@@ -1445,7 +1445,7 @@
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28" s="27"/>
+      <c r="B28" s="38"/>
       <c r="C28" s="22" t="s">
         <v>56</v>
       </c>
@@ -1469,7 +1469,7 @@
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="27"/>
+      <c r="B29" s="38"/>
       <c r="C29" s="24" t="s">
         <v>57</v>
       </c>
@@ -1493,7 +1493,7 @@
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="27"/>
+      <c r="B30" s="38"/>
       <c r="C30" s="20" t="s">
         <v>58</v>
       </c>
@@ -1520,7 +1520,7 @@
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="27"/>
+      <c r="B31" s="38"/>
       <c r="C31" s="16" t="s">
         <v>3</v>
       </c>
@@ -1547,7 +1547,7 @@
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="28"/>
+      <c r="B32" s="39"/>
       <c r="C32" s="17" t="s">
         <v>59</v>
       </c>
@@ -1569,7 +1569,7 @@
       </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="26" t="s">
+      <c r="B33" s="37" t="s">
         <v>61</v>
       </c>
       <c r="C33" s="13" t="s">
@@ -1595,7 +1595,7 @@
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="27"/>
+      <c r="B34" s="38"/>
       <c r="C34" s="22" t="s">
         <v>47</v>
       </c>
@@ -1619,7 +1619,7 @@
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="27"/>
+      <c r="B35" s="38"/>
       <c r="C35" s="22" t="s">
         <v>48</v>
       </c>
@@ -1643,7 +1643,7 @@
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="27"/>
+      <c r="B36" s="38"/>
       <c r="C36" s="22" t="s">
         <v>49</v>
       </c>
@@ -1667,7 +1667,7 @@
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B37" s="27"/>
+      <c r="B37" s="38"/>
       <c r="C37" s="22" t="s">
         <v>50</v>
       </c>
@@ -1691,7 +1691,7 @@
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B38" s="27"/>
+      <c r="B38" s="38"/>
       <c r="C38" s="22" t="s">
         <v>51</v>
       </c>
@@ -1715,7 +1715,7 @@
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="27"/>
+      <c r="B39" s="38"/>
       <c r="C39" s="22" t="s">
         <v>52</v>
       </c>
@@ -1739,7 +1739,7 @@
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="27"/>
+      <c r="B40" s="38"/>
       <c r="C40" s="22" t="s">
         <v>53</v>
       </c>
@@ -1763,7 +1763,7 @@
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="27"/>
+      <c r="B41" s="38"/>
       <c r="C41" s="22" t="s">
         <v>54</v>
       </c>
@@ -1787,7 +1787,7 @@
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="27"/>
+      <c r="B42" s="38"/>
       <c r="C42" s="22" t="s">
         <v>55</v>
       </c>
@@ -1811,7 +1811,7 @@
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B43" s="27"/>
+      <c r="B43" s="38"/>
       <c r="C43" s="22" t="s">
         <v>56</v>
       </c>
@@ -1835,7 +1835,7 @@
       </c>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B44" s="27"/>
+      <c r="B44" s="38"/>
       <c r="C44" s="24" t="s">
         <v>57</v>
       </c>
@@ -1859,7 +1859,7 @@
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B45" s="27"/>
+      <c r="B45" s="38"/>
       <c r="C45" s="20" t="s">
         <v>58</v>
       </c>
@@ -1886,7 +1886,7 @@
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B46" s="27"/>
+      <c r="B46" s="38"/>
       <c r="C46" s="16" t="s">
         <v>3</v>
       </c>
@@ -1913,7 +1913,7 @@
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B47" s="28"/>
+      <c r="B47" s="39"/>
       <c r="C47" s="17" t="s">
         <v>59</v>
       </c>
@@ -1992,10 +1992,10 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="40">
         <v>2021</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -2021,8 +2021,8 @@
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
       <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
@@ -2046,8 +2046,8 @@
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
       <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
@@ -2071,8 +2071,8 @@
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="5" t="s">
         <v>7</v>
       </c>
@@ -2096,8 +2096,8 @@
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
       <c r="D7" s="3" t="s">
         <v>17</v>
       </c>
@@ -2121,8 +2121,8 @@
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B8" s="30"/>
-      <c r="C8" s="30">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41">
         <v>2022</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -2148,8 +2148,8 @@
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
       <c r="D9" s="3" t="s">
         <v>5</v>
       </c>
@@ -2173,8 +2173,8 @@
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
       <c r="D10" s="3" t="s">
         <v>6</v>
       </c>
@@ -2198,8 +2198,8 @@
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
       <c r="D11" s="5" t="s">
         <v>7</v>
       </c>
@@ -2223,8 +2223,8 @@
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
       <c r="D12" s="3" t="s">
         <v>16</v>
       </c>
@@ -2248,10 +2248,10 @@
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="41">
         <v>2021</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -2277,8 +2277,8 @@
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
@@ -2302,8 +2302,8 @@
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
       <c r="D15" s="3" t="s">
         <v>6</v>
       </c>
@@ -2327,8 +2327,8 @@
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="5" t="s">
         <v>7</v>
       </c>
@@ -2352,8 +2352,8 @@
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
       <c r="D17" s="3" t="s">
         <v>15</v>
       </c>
@@ -2377,8 +2377,8 @@
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B18" s="30"/>
-      <c r="C18" s="30">
+      <c r="B18" s="41"/>
+      <c r="C18" s="41">
         <v>2022</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -2404,8 +2404,8 @@
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
       <c r="D19" s="3" t="s">
         <v>5</v>
       </c>
@@ -2429,8 +2429,8 @@
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
       <c r="D20" s="3" t="s">
         <v>6</v>
       </c>
@@ -2454,8 +2454,8 @@
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
       <c r="D21" s="5" t="s">
         <v>7</v>
       </c>
@@ -2479,8 +2479,8 @@
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
       <c r="D22" s="6" t="s">
         <v>16</v>
       </c>
@@ -2532,280 +2532,280 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="26" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="34">
+      <c r="C3" s="28">
         <v>3</v>
       </c>
-      <c r="D3" s="41">
+      <c r="D3" s="35">
         <v>30.93</v>
       </c>
-      <c r="E3" s="41">
+      <c r="E3" s="35">
         <v>0.23449</v>
       </c>
-      <c r="F3" s="41">
+      <c r="F3" s="35">
         <v>42.291800000000002</v>
       </c>
-      <c r="G3" s="38" t="s">
+      <c r="G3" s="32" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="40">
+      <c r="C4" s="34">
         <v>1</v>
       </c>
-      <c r="D4" s="41">
+      <c r="D4" s="35">
         <v>2.8610000000000002</v>
       </c>
-      <c r="E4" s="41">
+      <c r="E4" s="35">
         <v>2.1690000000000001E-2</v>
       </c>
-      <c r="F4" s="41">
+      <c r="F4" s="35">
         <v>11.7369</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="32" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="40">
+      <c r="C5" s="34">
         <v>11</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="35">
         <v>16.414000000000001</v>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="35">
         <v>0.12444</v>
       </c>
-      <c r="F5" s="41">
+      <c r="F5" s="35">
         <v>6.1211000000000002</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="G5" s="32" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="34">
         <v>1</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="35">
         <v>0.64100000000000001</v>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="35">
         <v>4.8599999999999997E-3</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="35">
         <v>2.6292</v>
       </c>
-      <c r="G6" s="38">
+      <c r="G6" s="32">
         <v>1.41E-2</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="34">
         <v>1</v>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="35">
         <v>0.38900000000000001</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="35">
         <v>2.9499999999999999E-3</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="35">
         <v>1.5976999999999999</v>
       </c>
-      <c r="G7" s="38">
+      <c r="G7" s="32">
         <v>0.1002</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="34">
         <v>1</v>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="35">
         <v>0.82599999999999996</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="35">
         <v>6.2599999999999999E-3</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="35">
         <v>3.3891</v>
       </c>
-      <c r="G8" s="38">
+      <c r="G8" s="32">
         <v>4.3E-3</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="34">
         <v>1</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="35">
         <v>0.64800000000000002</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="35">
         <v>4.9199999999999999E-3</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="35">
         <v>2.6594000000000002</v>
       </c>
-      <c r="G9" s="38">
+      <c r="G9" s="32">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="34">
         <v>1</v>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="35">
         <v>0.70799999999999996</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="35">
         <v>5.3699999999999998E-3</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="35">
         <v>2.9056999999999999</v>
       </c>
-      <c r="G10" s="38">
+      <c r="G10" s="32">
         <v>1.01E-2</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="34">
         <v>1</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="35">
         <v>1.0249999999999999</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="35">
         <v>7.77E-3</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="35">
         <v>4.2061000000000002</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G11" s="32">
         <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="34">
         <v>3</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="35">
         <v>3.2679999999999998</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="35">
         <v>2.478E-2</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="35">
         <v>4.4684999999999997</v>
       </c>
-      <c r="G12" s="38" t="s">
+      <c r="G12" s="32" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="40">
+      <c r="C13" s="34">
         <v>31</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="35">
         <v>11.183</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="35">
         <v>8.4779999999999994E-2</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="35">
         <v>1.4798</v>
       </c>
-      <c r="G13" s="38" t="s">
+      <c r="G13" s="32" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="40">
+      <c r="C14" s="34">
         <v>11</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="35">
         <v>3.0379999999999998</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="35">
         <v>2.3029999999999998E-2</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="35">
         <v>1.133</v>
       </c>
-      <c r="G14" s="38">
+      <c r="G14" s="32">
         <v>0.19239999999999999</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="30">
         <v>246</v>
       </c>
-      <c r="D15" s="42">
+      <c r="D15" s="36">
         <v>59.97</v>
       </c>
-      <c r="E15" s="42">
+      <c r="E15" s="36">
         <v>0.45465</v>
       </c>
-      <c r="F15" s="42"/>
-      <c r="G15" s="37"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
